--- a/Assets/Examples/ExcelCofig/item.xlsx
+++ b/Assets/Examples/ExcelCofig/item.xlsx
@@ -975,8 +975,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1002,6 +1002,14 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>333</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
